--- a/data/trans_orig/IP1020-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Edad-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6775</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6178</t>
+          <t>6844</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114605</t>
+          <t>115160</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>120698</t>
+          <t>120694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>221373</t>
+          <t>220707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226870</t>
+          <t>226864</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6399</t>
+          <t>6489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>246806</t>
+          <t>246716</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>252570</t>
+          <t>252573</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248685</t>
+          <t>248679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>498082</t>
+          <t>497504</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505064</t>
+          <t>505009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>4423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121467</t>
+          <t>122587</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264646</t>
+          <t>264640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>481</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1159</t>
+          <t>1161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7629</t>
+          <t>7256</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189238</t>
+          <t>189506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>200751</t>
+          <t>200973</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205567</t>
+          <t>205568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392517</t>
+          <t>392890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398987</t>
+          <t>398985</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2517</t>
+          <t>2582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10293</t>
+          <t>10688</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12282</t>
+          <t>11581</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>670728</t>
+          <t>670333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>678504</t>
+          <t>678439</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>710418</t>
+          <t>711119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>719424</t>
+          <t>719393</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1384823</t>
+          <t>1385165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396757</t>
+          <t>1396457</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10660</t>
+          <t>11649</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3426</t>
+          <t>3320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12431</t>
+          <t>12479</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>135621</t>
+          <t>134632</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143602</t>
+          <t>143578</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>139987</t>
+          <t>140571</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278363</t>
+          <t>278315</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287368</t>
+          <t>287474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>15325</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10181</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>23154</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218416</t>
+          <t>219151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229172</t>
+          <t>229589</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>256920</t>
+          <t>257137</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>264551</t>
+          <t>264756</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>479015</t>
+          <t>478422</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>492109</t>
+          <t>491956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,08%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>456</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5178</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>2057</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9532</t>
+          <t>9505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149656</t>
+          <t>149852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154373</t>
+          <t>154378</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>151125</t>
+          <t>151203</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157925</t>
+          <t>157893</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303873</t>
+          <t>303900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311478</t>
+          <t>311348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3714,7 +3714,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5924</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>166887</t>
+          <t>167081</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172727</t>
+          <t>174312</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343370</t>
+          <t>343380</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348700</t>
+          <t>348698</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12212</t>
+          <t>11700</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26476</t>
+          <t>25770</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5933</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17055</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>40005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>680452</t>
+          <t>681158</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>694716</t>
+          <t>695228</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>731087</t>
+          <t>731200</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>742209</t>
+          <t>742211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1416537</t>
+          <t>1415065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1434666</t>
+          <t>1433745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5026</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6431</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1868</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8995</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>126900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117733</t>
+          <t>117705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123513</t>
+          <t>123501</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>246823</t>
+          <t>247232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>253950</t>
+          <t>253975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1089</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1653</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9047</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3804</t>
+          <t>4313</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203689</t>
+          <t>203331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209428</t>
+          <t>209000</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249014</t>
+          <t>249876</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256408</t>
+          <t>256490</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455855</t>
+          <t>455286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464774</t>
+          <t>464265</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2094</t>
+          <t>2145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10516</t>
+          <t>10791</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>182658</t>
+          <t>182995</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>188210</t>
+          <t>188265</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180780</t>
+          <t>181248</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187880</t>
+          <t>187872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366955</t>
+          <t>366680</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375377</t>
+          <t>375326</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>618</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6075</t>
+          <t>5699</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2056</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9350</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>167226</t>
+          <t>167602</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>172690</t>
+          <t>172683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167220</t>
+          <t>167836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>173380</t>
+          <t>173379</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337998</t>
+          <t>337839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345334</t>
+          <t>345292</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15438</t>
+          <t>15234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19103</t>
+          <t>19954</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15338</t>
+          <t>15728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30510</t>
+          <t>31162</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>688933</t>
+          <t>689137</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>698911</t>
+          <t>699025</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725741</t>
+          <t>724890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>737586</t>
+          <t>737187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1418705</t>
+          <t>1418053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433877</t>
+          <t>1433487</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>55</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>4790</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52425</t>
+          <t>52440</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57052</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113968</t>
+          <t>114165</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118494</t>
+          <t>118900</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>2725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21658</t>
+          <t>22542</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147367</t>
+          <t>148599</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>156518</t>
+          <t>156574</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167436</t>
+          <t>167470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177476</t>
+          <t>177724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>320195</t>
+          <t>319311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>332539</t>
+          <t>332588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2894</t>
+          <t>3274</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17294</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10871</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24535</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160843</t>
+          <t>160728</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>170178</t>
+          <t>169798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195301</t>
+          <t>195196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>206935</t>
+          <t>207175</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>360588</t>
+          <t>361028</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374692</t>
+          <t>375230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4125</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>15302</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11139</t>
+          <t>11841</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8470</t>
+          <t>8749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21373</t>
+          <t>22609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260562</t>
+          <t>260156</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>271333</t>
+          <t>271432</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>294344</t>
+          <t>293642</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>303251</t>
+          <t>302869</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>559567</t>
+          <t>558331</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572470</t>
+          <t>572191</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15613</t>
+          <t>14743</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>32889</t>
+          <t>31410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34309</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36197</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59866</t>
+          <t>59673</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>632451</t>
+          <t>633930</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>649727</t>
+          <t>650597</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727204</t>
+          <t>727663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744543</t>
+          <t>744859</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367446</t>
+          <t>1367639</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1391115</t>
+          <t>1390731</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,44%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1020-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP1020-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,92 +723,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>686</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6760</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2721</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>686</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6220</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>675</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>118659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114620</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120694</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,76%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>118659</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>115160</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>120694</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,88%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>340</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220707</t>
+          <t>220783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226864</t>
+          <t>226876</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1890</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5572</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>2573</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>632</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6489</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6414</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1890</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5077</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9457</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>251866</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>248184</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>253158</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>250632</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>246716</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>252573</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>246791</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>252492</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,98%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>251866</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>248679</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>253159</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>497504</t>
+          <t>497926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>505009</t>
+          <t>505056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1439</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4961</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5139</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,13%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1439</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5001</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1439</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4423</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1522,74 +1522,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126109</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>122587</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>122409</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,87%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,97%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>401</t>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264640</t>
+          <t>264062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1842</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5039</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1375</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4591</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4279</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1842</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>481</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5076</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1170</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>204207</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>201010</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>205567</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>284</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>192722</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>189506</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>189818</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,8%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>204207</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>200973</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>205568</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,77%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>591</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>392890</t>
+          <t>392882</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>398985</t>
+          <t>398976</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6453</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11189</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2582</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10688</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2129</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>10536</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6453</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3307</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11581</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18556</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1076</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>716247</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>711511</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>719475</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1010</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>675634</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670333</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>678439</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670485</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>678892</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>99,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1076</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>716247</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>711119</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>719393</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385165</t>
+          <t>1385616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1396457</t>
+          <t>1396468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4018</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>5716</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2703</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11649</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2603</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11139</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3942</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12479</t>
+          <t>12182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,19%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>143225</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>140495</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>210</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>140565</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>134632</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>143578</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>135142</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>143678</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>96,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>92,04%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,15%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>143225</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>140571</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>278315</t>
+          <t>278612</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287474</t>
+          <t>287634</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>144513</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>146281</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>144513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5516</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2787</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9403</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>15325</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16002</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5516</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9964</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23154</t>
+          <t>22493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>261585</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>256100</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>264314</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,93%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>324</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>225073</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>219151</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>229589</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>218474</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>229127</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,99%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,46%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>363</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>261585</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>257137</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>264756</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,93%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>478422</t>
+          <t>479083</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>491956</t>
+          <t>491786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,05%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>371</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>267101</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>337</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>234476</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>371</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>267101</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1885</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2903</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>678</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7368</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2057</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155668</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>151427</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>157613</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,17%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152949</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149852</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154378</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>149504</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154373</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,78%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,78%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>155668</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>151203</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>157893</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303900</t>
+          <t>303690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311348</t>
+          <t>311574</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154834</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1273</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,74%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3645</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5914</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -3812,74 +3812,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>177190</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>173326</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>170064</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167081</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167332</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,26%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,66%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>177190</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>174312</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,95%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>502</t>
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>343380</t>
+          <t>343668</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>348698</t>
+          <t>348699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>177957</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>177957</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>10473</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16679</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>18278</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>11700</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25770</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>12126</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,59%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>10473</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>5931</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>16942</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40005</t>
+          <t>38030</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>737669</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>731463</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>742340</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,77%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>688650</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>681158</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>695228</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>680914</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>694802</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,41%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,35%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>737669</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>731200</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>742211</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1415065</t>
+          <t>1417040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433745</t>
+          <t>1433769</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2604</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5969</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1794</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4754</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5247</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2604</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>663</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1843</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>121560</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>118195</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123515</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,19%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>208</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>129860</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>126900</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>131118</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>126407</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>131122</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,64%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>121560</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>117705</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>123501</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247232</t>
+          <t>247048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>253975</t>
+          <t>253979</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4965,67 +4965,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>4208</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1375</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>9015</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>3305</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1517</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7186</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6982</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4208</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1571</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8185</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13292</t>
+          <t>12351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>253853</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249046</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>256686</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,47%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>326</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>207212</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>203331</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>209000</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>203535</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>209410</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>98,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>253853</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>249876</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>256490</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>455286</t>
+          <t>456227</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>464265</t>
+          <t>464675</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3148</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8002</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2123</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5904</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3148</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7324</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2145</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>185424</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>180570</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187864</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,33%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>186776</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>182995</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>188265</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>182967</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>188268</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,88%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,66%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>185424</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>181248</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187872</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>366680</t>
+          <t>367378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375326</t>
+          <t>375384</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2745</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6315</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,58%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2051</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5699</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5477</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2745</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>6212</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,58%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9509</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>171303</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>167733</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>173347</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,42%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,37%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>171250</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>167602</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>172683</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>167824</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>172689</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>171303</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>167836</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>173379</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,42%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>337839</t>
+          <t>337681</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345292</t>
+          <t>345319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12706</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7671</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>20758</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9273</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5346</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15234</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15348</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,32%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>12706</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>7657</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>19954</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15728</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31162</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1047</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>732138</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>724086</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>737173</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,29%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1046</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>695098</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>689137</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>699025</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>689023</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>699086</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,68%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,24%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1047</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>732138</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>724890</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>737187</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1418053</t>
+          <t>1418510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1433487</t>
+          <t>1433468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1787</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5071</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>489</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>474</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55724</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52440</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>57045</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,89%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,18%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>50290</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>47187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51601</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>117168</t>
+          <t>100827</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114165</t>
+          <t>97871</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>102153</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7958</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4346</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13507</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>5783</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10700</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>5636</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15084</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>14599</t>
+          <t>13593</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22542</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>149564</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144015</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>153176</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,95%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>153516</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>148599</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>156574</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,29%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>173738</t>
+          <t>139882</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167470</t>
+          <t>134005</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177724</t>
+          <t>142788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>327254</t>
+          <t>289446</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>319311</t>
+          <t>282296</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>332588</t>
+          <t>294613</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9814</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5087</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16937</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,46%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6613</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3274</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12344</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>3566</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17294</t>
+          <t>13067</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16782</t>
+          <t>16746</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>24696</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>190312</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>183189</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>195039</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,54%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,46%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>166459</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160728</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>169798</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,18%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>202322</t>
+          <t>167740</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>195196</t>
+          <t>161605</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207175</t>
+          <t>171106</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>368781</t>
+          <t>358052</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>361028</t>
+          <t>350102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>375230</t>
+          <t>364455</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,24%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6114</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2691</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12576</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8147</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4026</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15302</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5787</t>
+          <t>8714</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2614</t>
+          <t>4241</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>16204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13935</t>
+          <t>14829</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>22819</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>286531</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>280069</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>289954</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,7%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>267311</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>260156</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>271432</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>97,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>299696</t>
+          <t>247839</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293642</t>
+          <t>240349</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>302869</t>
+          <t>252312</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>567005</t>
+          <t>534369</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558331</t>
+          <t>526379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>572191</t>
+          <t>540387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>23886</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>16439</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>33216</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>22331</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>14743</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31410</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>23082</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>34309</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>47102</t>
+          <t>46968</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36581</t>
+          <t>35412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59673</t>
+          <t>59721</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>676943</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667613</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684390</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,59%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>910</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>643009</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>633930</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>650597</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>96,64%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>943</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>737201</t>
+          <t>605751</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>727663</t>
+          <t>595786</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744859</t>
+          <t>613040</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1380210</t>
+          <t>1282694</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1367639</t>
+          <t>1269941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1390731</t>
+          <t>1294250</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1427312</t>
+          <t>1329662</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
